--- a/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_DATA_CLEANING.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_DATA_CLEANING.xlsx
@@ -453,19 +453,19 @@
         <v>Outliers là những giá trị dị biệt, nằm cách xa phần lớn các điểm dữ liệu khác trong mẫu (ví dụ: tuổi nhân viên nhập là 200). Outliers có thể do sai sót nhập liệu hoặc là giá trị đặc biệt thực tế.</v>
       </c>
       <c r="E2" t="str">
+        <v>Các hàng dữ liệu bị trống hoàn toàn không chứa bất kỳ thông tin nào — dữ liệu khuyết thiếu null</v>
+      </c>
+      <c r="F2" t="str">
         <v>Các giá trị dữ liệu khác biệt quá lớn, lệch chuẩn hẳn so với phần lớn các quan trắc khác trong bộ dữ liệu — giá trị lệch chuẩn dị biệt</v>
       </c>
-      <c r="F2" t="str">
-        <v>Các hàng dữ liệu bị trống hoàn toàn không chứa bất kỳ thông tin nào — dữ liệu khuyết thiếu null</v>
-      </c>
       <c r="G2" t="str">
+        <v>Các câu lệnh SQL bị viết sai cú pháp khiến truy vấn không thể thực thi — lỗi cú pháp truy vấn</v>
+      </c>
+      <c r="H2" t="str">
         <v>Các trường dữ liệu chứa thông tin nhạy cảm của khách hàng cần được mã hóa bảo mật — dữ liệu nhạy cảm</v>
       </c>
-      <c r="H2" t="str">
-        <v>Các câu lệnh SQL bị viết sai cú pháp khiến truy vấn không thể thực thi — lỗi cú pháp truy vấn</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>Đối với biến số liên tục như Tuổi, việc thay thế NULL bằng giá trị trung bình (mean) hoặc trung vị (median) là kỹ thuật điền khuyết (Imputation) cơ bản để giữ lại dòng dữ liệu phục vụ phân tích.</v>
       </c>
       <c r="E3" t="str">
-        <v>Điền giá trị mặc định là tuổi trung bình (mean) hoặc trung vị (median) của toàn bộ khách hàng có sẵn — điền giá trị đại diện</v>
+        <v>Bắt buộc người dùng phải gửi ảnh chụp căn cước công dân để hệ thống tự động trích xuất lại tuổi — yêu cầu xác thực cưỡng bức</v>
       </c>
       <c r="F3" t="str">
         <v>Xóa bỏ vĩnh viễn toàn bộ cơ sở dữ liệu của dự án và yêu cầu khách hàng đăng ký lại từ đầu — xóa database</v>
@@ -491,10 +491,10 @@
         <v>Tự động sinh ngẫu nhiên một con số từ 1 đến 100 để điền vào ô trống đó — sinh số ngẫu nhiên</v>
       </c>
       <c r="H3" t="str">
-        <v>Bắt buộc người dùng phải gửi ảnh chụp căn cước công dân để hệ thống tự động trích xuất lại tuổi — yêu cầu xác thực cưỡng bức</v>
+        <v>Điền giá trị mặc định là tuổi trung bình (mean) hoặc trung vị (median) của toàn bộ khách hàng có sẵn — điền giá trị đại diện</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>`isnull()` và `isna()` là hai hàm tương đương trong Pandas dùng để kiểm tra và phát hiện sự hiện diện của giá trị NULL/NaN trong dữ liệu.</v>
       </c>
       <c r="E4" t="str">
-        <v>isnull() hoặc isna() — trả về DataFrame dạng Boolean biểu thị ô nào bị khuyết — phát hiện giá trị khuyết</v>
+        <v>describe() — dùng để tính toán các thống kê mô tả cơ bản của DataFrame — thống kê mô tả</v>
       </c>
       <c r="F4" t="str">
         <v>dropna() — dùng để xóa bỏ trực tiếp các dòng chứa giá trị khuyết khỏi DataFrame — xóa dòng khuyết</v>
       </c>
       <c r="G4" t="str">
+        <v>isnull() hoặc isna() — trả về DataFrame dạng Boolean biểu thị ô nào bị khuyết — phát hiện giá trị khuyết</v>
+      </c>
+      <c r="H4" t="str">
         <v>fillna() — dùng để thay thế các giá trị khuyết bằng một giá trị chỉ định trước — điền giá trị khuyết</v>
       </c>
-      <c r="H4" t="str">
-        <v>describe() — dùng để tính toán các thống kê mô tả cơ bản của DataFrame — thống kê mô tả</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Trim/Strip giúp làm sạch chuỗi nhập liệu bị thừa khoảng trắng do người dùng gõ nhầm (ví dụ: " nguyen van a " -&gt; "nguyen van a"), giúp việc so sánh chuỗi chính xác.</v>
       </c>
       <c r="E5" t="str">
+        <v>Mã hóa chuỗi văn bản thành một chuỗi ký tự bảo mật không thể đọc được — mã hóa chuỗi</v>
+      </c>
+      <c r="F5" t="str">
         <v>Loại bỏ các khoảng trắng thừa ở đầu và cuối của chuỗi văn bản — loại bỏ khoảng trắng thừa</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Chuyển đổi toàn bộ chuỗi văn bản từ chữ thường sang chữ hoa in đậm — in hoa chuỗi</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Cắt chuỗi văn bản ra thành nhiều chuỗi con dựa trên ký tự ngăn cách — cắt chuỗi</v>
       </c>
-      <c r="H5" t="str">
-        <v>Mã hóa chuỗi văn bản thành một chuỗi ký tự bảo mật không thể đọc được — mã hóa chuỗi</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Trùng lặp dữ liệu khiến các phép tính SUM, COUNT bị cộng lặp, dẫn đến việc đưa ra các báo cáo phân tích sai lệch nghiêm trọng về quy mô thực tế.</v>
       </c>
       <c r="E6" t="str">
-        <v>Làm sai lệch kết quả thống kê tổng hợp (như thổi phồng số lượng khách hàng thực tế và tổng doanh thu) — sai lệch số liệu tổng</v>
+        <v>Làm hỏng ổ cứng vật lý lưu trữ cơ sở dữ liệu của máy chủ dự án — hỏng phần cứng</v>
       </c>
       <c r="F6" t="str">
-        <v>Làm hỏng ổ cứng vật lý lưu trữ cơ sở dữ liệu của máy chủ dự án — hỏng phần cứng</v>
+        <v>Làm cho giao diện hiển thị của dashboard bị chuyển sang chế độ ban đêm — thay đổi giao diện</v>
       </c>
       <c r="G6" t="str">
         <v>Tự động đổi mật khẩu đăng nhập của tất cả các khách hàng bị trùng lặp — lỗi đăng nhập</v>
       </c>
       <c r="H6" t="str">
-        <v>Làm cho giao diện hiển thị của dashboard bị chuyển sang chế độ ban đêm — thay đổi giao diện</v>
+        <v>Làm sai lệch kết quả thống kê tổng hợp (như thổi phồng số lượng khách hàng thực tế và tổng doanh thu) — sai lệch số liệu tổng</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Hàm `drop_duplicates()` loại bỏ nhanh các dòng trùng lặp hoàn toàn hoặc trùng lặp trên một tập hợp các cột chỉ định.</v>
       </c>
       <c r="E7" t="str">
-        <v>drop_duplicates() — loại bỏ các dòng bị trùng lặp và giữ lại dòng đầu tiên hoặc cuối cùng — xóa trùng lặp</v>
+        <v>dropna() — xóa bỏ các dòng chứa giá trị bị khuyết thiếu khỏi DataFrame — xóa dòng khuyết</v>
       </c>
       <c r="F7" t="str">
         <v>duplicated() — trả về mảng Boolean đánh dấu các dòng bị trùng lặp trong DataFrame — phát hiện trùng lặp</v>
       </c>
       <c r="G7" t="str">
-        <v>dropna() — xóa bỏ các dòng chứa giá trị bị khuyết thiếu khỏi DataFrame — xóa dòng khuyết</v>
+        <v>drop_duplicates() — loại bỏ các dòng bị trùng lặp và giữ lại dòng đầu tiên hoặc cuối cùng — xóa trùng lặp</v>
       </c>
       <c r="H7" t="str">
         <v>unique() — trả về danh sách các giá trị độc nhất trong một cột dữ liệu — lấy giá trị độc nhất</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Excel cung cấp tính năng "Remove Duplicates" giúp người dùng chọn các cột cần đối chiếu để tìm và xóa dòng trùng lặp chỉ qua vài click chuột.</v>
       </c>
       <c r="E8" t="str">
+        <v>Conditional Formatting (nằm trong tab Home) — công cụ tô màu đánh dấu dữ liệu trùng</v>
+      </c>
+      <c r="F8" t="str">
         <v>Remove Duplicates (nằm trong tab Data) — công cụ xóa trùng lặp tự động</v>
       </c>
-      <c r="F8" t="str">
-        <v>Conditional Formatting (nằm trong tab Home) — công cụ tô màu đánh dấu dữ liệu trùng</v>
-      </c>
       <c r="G8" t="str">
+        <v>Data Validation (nằm trong tab Data) — công cụ ràng buộc điều kiện nhập liệu</v>
+      </c>
+      <c r="H8" t="str">
         <v>Text to Columns (nằm trong tab Data) — công cụ chia tách chuỗi dữ liệu trong ô</v>
       </c>
-      <c r="H8" t="str">
-        <v>Data Validation (nằm trong tab Data) — công cụ ràng buộc điều kiện nhập liệu</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Không nhất quán định dạng là lỗi rất phổ biến khi thu thập dữ liệu từ nhiều nguồn hoặc do người dùng tự nhập tay không có ràng buộc (regex validation).</v>
       </c>
       <c r="E9" t="str">
+        <v>Số điện thoại của tất cả các khách hàng đều bắt đầu bằng chữ số 0 — quy định đầu số</v>
+      </c>
+      <c r="F9" t="str">
         <v>Một số dòng lưu dạng `0901234567`, số khác lưu dạng `+84901234567` hoặc `090-123-4567` — không nhất quán định dạng</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Số điện thoại của khách hàng có chứa đúng 10 chữ số tự nhiên — định dạng chuẩn</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Số điện thoại của tất cả các khách hàng đều bắt đầu bằng chữ số 0 — quy định đầu số</v>
       </c>
       <c r="H9" t="str">
         <v>Cột số điện thoại được lưu trữ dưới kiểu dữ liệu chuỗi văn bản (String) — kiểu dữ liệu chuẩn</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Outliers không phải lúc nào cũng là lỗi nhập liệu. Trong phân tích gian lận (Fraud Detection), chính các giao dịch Outlier (số tiền giao dịch cực lớn, vị trí địa lý bất thường) là tiêu điểm cần tìm kiếm. DA phải phân tích nguồn gốc của Outlier trước khi quyết định xử lý.</v>
       </c>
       <c r="E10" t="str">
+        <v>Vì Outlier là các giá trị bắt buộc phải có để tính toán hệ số tương quan của mô hình hồi quy — yêu cầu thống kê</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Vì khách hàng sẽ khiếu nại nếu họ phát hiện ra tài khoản của họ bị hệ thống đánh dấu là Outlier — khiếu nại khách hàng</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Vì việc xóa Outlier sẽ tự động làm hỏng cấu trúc logic của cơ sở dữ liệu quan hệ — hỏng database</v>
+      </c>
+      <c r="H10" t="str">
         <v>Vì Outlier có thể chứa đựng những thông tin thực tế quan trọng (như giao dịch gian lận tài chính, sự cố hệ thống); xóa bỏ sẽ làm mất đi các insight dị biệt này — Outlier mang giá trị thông tin đặc biệt</v>
       </c>
-      <c r="F10" t="str">
-        <v>Vì việc xóa Outlier sẽ tự động làm hỏng cấu trúc logic của cơ sở dữ liệu quan hệ — hỏng database</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Vì Outlier là các giá trị bắt buộc phải có để tính toán hệ số tương quan của mô hình hồi quy — yêu cầu thống kê</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Vì khách hàng sẽ khiếu nại nếu họ phát hiện ra tài khoản của họ bị hệ thống đánh dấu là Outlier — khiếu nại khách hàng</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>MICE là kỹ thuật điền khuyết tiên tiến. Thay vì chỉ tính trung bình đơn giản trên 1 cột (Univariate), MICE xem xét giá trị của các cột khác để dự báo giá trị khuyết thiếu một cách khoa học, giữ lại phân phối tự nhiên của dữ liệu.</v>
       </c>
       <c r="E11" t="str">
-        <v>MICE ước tính giá trị bị khuyết của một biến dựa trên các mối quan hệ tương quan với các biến khác trong bộ dữ liệu thông qua mô hình dự báo hồi quy lặp đi lặp lại — điền khuyết đa biến đệ quy</v>
+        <v>MICE gửi yêu cầu API tự động sang hệ thống bên thứ ba để xin lại dữ liệu bị mất — tích hợp API lấy lại dữ liệu</v>
       </c>
       <c r="F11" t="str">
         <v>MICE điền nhanh số 0 hoặc giá trị trung vị vào tất cả các ô bị trống một cách ngẫu nhiên — điền giá trị đơn giản</v>
       </c>
       <c r="G11" t="str">
-        <v>MICE gửi yêu cầu API tự động sang hệ thống bên thứ ba để xin lại dữ liệu bị mất — tích hợp API lấy lại dữ liệu</v>
+        <v>MICE sử dụng trí tuệ nhân tạo AI để tự vẽ lại hình ảnh chân dung của khách hàng bị thiếu — vẽ ảnh thiếu</v>
       </c>
       <c r="H11" t="str">
-        <v>MICE sử dụng trí tuệ nhân tạo AI để tự vẽ lại hình ảnh chân dung của khách hàng bị thiếu — vẽ ảnh thiếu</v>
+        <v>MICE ước tính giá trị bị khuyết của một biến dựa trên các mối quan hệ tương quan với các biến khác trong bộ dữ liệu thông qua mô hình dự báo hồi quy lặp đi lặp lại — điền khuyết đa biến đệ quy</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Hàm `pd.to_datetime()` của Pandas cực kỳ mạnh mẽ, nó có thể tự động nhận diện và chuyển đổi nhiều định dạng ngày tháng khác nhau về kiểu dữ liệu `datetime64[ns]` chuẩn. Tham số `errors='coerce'` giúp chuyển các dòng bị lỗi cú pháp nặng (không thể parse) thành NaT (Not a Time) thay vì làm sập chương trình.</v>
       </c>
       <c r="E12" t="str">
+        <v>Viết các câu lệnh chuỗi cắt ghép bằng hàm `.split()` dựa trên ký tự gạch chéo để trích xuất ngày, tháng, năm — cắt ghép chuỗi thủ công</v>
+      </c>
+      <c r="F12" t="str">
         <v>Sử dụng hàm `pd.to_datetime(column, errors='coerce')` để Pandas tự động phân tích cú pháp và chuyển đổi về định dạng chuẩn — tự động parse datetime</v>
       </c>
-      <c r="F12" t="str">
-        <v>Viết các câu lệnh chuỗi cắt ghép bằng hàm `.split()` dựa trên ký tự gạch chéo để trích xuất ngày, tháng, năm — cắt ghép chuỗi thủ công</v>
-      </c>
       <c r="G12" t="str">
+        <v>Yêu cầu lập trình viên Frontend khóa tính năng chọn ngày trên giao diện của trang web — khóa giao diện</v>
+      </c>
+      <c r="H12" t="str">
         <v>Xóa bỏ toàn bộ các dòng có định dạng ngày tháng không khớp với dòng đầu tiên của bảng — xóa dòng định dạng lệch</v>
       </c>
-      <c r="H12" t="str">
-        <v>Yêu cầu lập trình viên Frontend khóa tính năng chọn ngày trên giao diện của trang web — khóa giao diện</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -772,10 +772,10 @@
         <v>Quy tắc IQR định nghĩa: $IQR = Q_3 - Q_1$. Ranh giới dưới là $Q_1 - 1.5 \cdot IQR$, ranh giới trên là $Q_3 + 1.5 \cdot IQR$. Bất kỳ điểm dữ liệu nào nằm ngoài khoảng ranh giới này đều được thuật toán của Box Plot đánh dấu là Outlier.</v>
       </c>
       <c r="E13" t="str">
+        <v>Các điểm dữ liệu nằm bên trong khu vực hộp giữa phân vị 25 ($Q_1$) và phân vị 75 ($Q_3$) — vùng hộp trung tâm</v>
+      </c>
+      <c r="F13" t="str">
         <v>Các điểm nằm ngoài khoảng từ $Q_1 - 1.5 \cdot IQR$ đến $Q_3 + 1.5 \cdot IQR$ — ranh giới IQR</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Các điểm dữ liệu nằm bên trong khu vực hộp giữa phân vị 25 ($Q_1$) và phân vị 75 ($Q_3$) — vùng hộp trung tâm</v>
       </c>
       <c r="G13" t="str">
         <v>Các điểm dữ liệu có giá trị lớn hơn giá trị trung bình cộng của bộ mẫu dữ liệu — lớn hơn trung bình</v>
@@ -784,7 +784,7 @@
         <v>Các điểm dữ liệu có tần suất xuất hiện trùng lặp nhiều nhất trong bảng — tần suất trùng lặp cao</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Lệch chuẩn dữ liệu chữ (Text inconsistency) do thiếu ràng buộc nhập liệu. BA/DA phải thiết lập bảng ánh xạ (ví dụ: {"nam": "Nam", "M": "Nam", "nu": "Nữ", "F": "Nữ"}) để đưa dữ liệu phân loại về định dạng nhất quán trước khi phân tích nhóm.</v>
       </c>
       <c r="E14" t="str">
+        <v>Thay thế tất cả các giá trị giới tính bằng giá trị xuất hiện nhiều nhất (mode) mà không cần phân loại — điền mode cưỡng bức</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Tự động đổi tất cả các giá trị giới tính sang dạng số nguyên tự tăng bắt đầu từ số 1 — số hóa tự tăng</v>
+      </c>
+      <c r="G14" t="str">
         <v>Ánh xạ (Mapping) chuyển đổi tất cả về một bộ giá trị chuẩn thống nhất (ví dụ: `Nam` / `Nữ` hoặc `M` / `F`), và xử lý các giá trị trống (NULL) theo quy tắc nghiệp vụ — chuẩn hóa ánh xạ dữ liệu phân loại</v>
       </c>
-      <c r="F14" t="str">
+      <c r="H14" t="str">
         <v>Xóa bỏ toàn bộ các dòng chứa giá trị `M` và `F` vì chúng là ký tự tiếng Anh không phù hợp — xóa bỏ dòng tiếng Anh</v>
       </c>
-      <c r="G14" t="str">
-        <v>Thay thế tất cả các giá trị giới tính bằng giá trị xuất hiện nhiều nhất (mode) mà không cần phân loại — điền mode cưỡng bức</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Tự động đổi tất cả các giá trị giới tính sang dạng số nguyên tự tăng bắt đầu từ số 1 — số hóa tự tăng</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -836,10 +836,10 @@
         <v>Xóa bỏ hoàn toàn các dòng dữ liệu chứa Outliers khỏi DataFrame — xóa dòng ngoại lai</v>
       </c>
       <c r="G15" t="str">
+        <v>Chuyển đổi toàn bộ Outliers thành giá trị NULL để thuật toán tự động bỏ qua khi chạy — chuyển thành NULL</v>
+      </c>
+      <c r="H15" t="str">
         <v>Cộng thêm một hằng số cố định vào tất cả các Outliers để đưa chúng về gần giá trị trung bình — cộng hằng số hiệu chỉnh</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Chuyển đổi toàn bộ Outliers thành giá trị NULL để thuật toán tự động bỏ qua khi chạy — chuyển thành NULL</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>MCAR là trường hợp lý tưởng (ví dụ: đánh rơi tệp khảo sát ngẫu nhiên). MNAR là trường hợp phức tạp (ví dụ: người có thu nhập rất cao thường từ chối khai báo thu nhập trong khảo sát, làm biến thu nhập bị khuyết phụ thuộc vào giá trị thu nhập thực tế). Xử lý MNAR đòi hỏi mô hình hóa phức tạp hơn.</v>
       </c>
       <c r="E16" t="str">
+        <v>MCAR do lỗi lập trình viên viết code sai; MNAR do máy chủ bị mất kết nối mạng internet — nguyên nhân kỹ thuật</v>
+      </c>
+      <c r="F16" t="str">
+        <v>MCAR có thể tự động sửa lỗi; MNAR bắt buộc phải xóa bỏ bảng dữ liệu đó đi — khả năng sửa lỗi</v>
+      </c>
+      <c r="G16" t="str">
+        <v>MCAR chỉ xảy ra ở dữ liệu số; MNAR chỉ xảy ra ở dữ liệu chuỗi văn bản chữ — kiểu dữ liệu bị khuyết</v>
+      </c>
+      <c r="H16" t="str">
         <v>MCAR: Dữ liệu khuyết thiếu hoàn toàn ngẫu nhiên không phụ thuộc vào bất kỳ biến nào; MNAR: Dữ liệu khuyết thiếu có chủ đích, phụ thuộc trực tiếp vào chính giá trị của biến bị thiếu đó — ngẫu nhiên khách quan vs chủ quan hệ thống</v>
       </c>
-      <c r="F16" t="str">
-        <v>MCAR chỉ xảy ra ở dữ liệu số; MNAR chỉ xảy ra ở dữ liệu chuỗi văn bản chữ — kiểu dữ liệu bị khuyết</v>
-      </c>
-      <c r="G16" t="str">
-        <v>MCAR do lỗi lập trình viên viết code sai; MNAR do máy chủ bị mất kết nối mạng internet — nguyên nhân kỹ thuật</v>
-      </c>
-      <c r="H16" t="str">
-        <v>MCAR có thể tự động sửa lỗi; MNAR bắt buộc phải xóa bỏ bảng dữ liệu đó đi — khả năng sửa lỗi</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -891,10 +891,10 @@
         <v>Min-Max đưa dữ liệu về khoảng cố định [0, 1]; Standardization đưa dữ liệu về phân phối có trung bình bằng 0 và độ lệch chuẩn bằng 1 — [0, 1] vs Phân phối chuẩn</v>
       </c>
       <c r="F17" t="str">
+        <v>Min-Max do BA tự tính tay; Standardization bắt buộc phải chạy bằng thư viện Python — phân vai trò tính toán</v>
+      </c>
+      <c r="G17" t="str">
         <v>Min-Max chỉ áp dụng cho số nguyên dương; Standardization chỉ áp dụng cho số nguyên âm — giới hạn miền số</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Min-Max do BA tự tính tay; Standardization bắt buộc phải chạy bằng thư viện Python — phân vai trò tính toán</v>
       </c>
       <c r="H17" t="str">
         <v>Min-Max làm tăng kích thước tệp tin dữ liệu; Standardization làm giảm dung lượng tệp tin — tác động bộ nhớ</v>
@@ -917,19 +917,19 @@
         <v>Nội suy (Interpolation) là kỹ thuật điền khuyết đắc lực cho chuỗi thời gian (ví dụ: nhiệt độ đo theo giờ bị mất dữ liệu lúc 10h, hệ thống sẽ lấy trung bình giữa 9h và 11h để điền vào, giúp giữ tính liên tục của biểu đồ).</v>
       </c>
       <c r="E18" t="str">
-        <v>Ước tính giá trị khuyết bằng phép nội suy tuyến tính dựa trên các giá trị của các bản ghi liền trước và liền sau (thích hợp cho dữ liệu chuỗi thời gian - Time Series) — nội suy tuyến tính chuỗi thời gian</v>
+        <v>Xóa bỏ toàn bộ các dòng chứa giá trị khuyết thiếu khỏi DataFrame — xóa dòng chứa khuyết</v>
       </c>
       <c r="F18" t="str">
         <v>Thay thế giá trị khuyết bằng giá trị trung bình của toàn bộ cột dữ liệu đó — điền giá trị trung bình</v>
       </c>
       <c r="G18" t="str">
-        <v>Xóa bỏ toàn bộ các dòng chứa giá trị khuyết thiếu khỏi DataFrame — xóa dòng chứa khuyết</v>
+        <v>Ước tính giá trị khuyết bằng phép nội suy tuyến tính dựa trên các giá trị của các bản ghi liền trước và liền sau (thích hợp cho dữ liệu chuỗi thời gian - Time Series) — nội suy tuyến tính chuỗi thời gian</v>
       </c>
       <c r="H18" t="str">
         <v>Tự động gọi API để cập nhật lại dữ liệu từ hệ thống nguồn — cập nhật dữ liệu tự động</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -949,13 +949,13 @@
         <v>Lọc bỏ các Outliers cực trị dựa trên ngưỡng vật lý (nhiệt độ phòng không thể vượt quá 100 độ C), thay thế Outliers và các giá trị NULL bằng phương pháp nội suy tuyến tính (Linear Interpolation) dựa trên các giây liền kề — lọc vật lý và nội suy chuỗi thời gian</v>
       </c>
       <c r="F19" t="str">
+        <v>Điền giá trị trung bình (mean) của toàn bộ nhiệt độ đo được trong một tháng vào tất cả các ô bị trống và ô Outlier — điền trung bình tháng làm mất đặc trưng cục bộ</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Giữ nguyên bộ dữ liệu thô vì mô hình dự báo AI sẽ tự động học cách bỏ qua các giá trị nhiễu này — chủ quan không xử lý nhiễu</v>
+      </c>
+      <c r="H19" t="str">
         <v>Xóa bỏ toàn bộ các dòng chứa dữ liệu khuyết thiếu và Outliers khỏi bộ dữ liệu — xóa bỏ bản ghi thô làm mất tính liên tục thời gian</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Điền giá trị trung bình (mean) của toàn bộ nhiệt độ đo được trong một tháng vào tất cả các ô bị trống và ô Outlier — điền trung bình tháng làm mất đặc trưng cục bộ</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Giữ nguyên bộ dữ liệu thô vì mô hình dự báo AI sẽ tự động học cách bỏ qua các giá trị nhiễu này — chủ quan không xử lý nhiễu</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -978,13 +978,13 @@
         <v>Chuyển về chữ thường, loại bỏ ký tự đặc biệt/dấu câu, tách từ tiếng Việt (Word Segmentation), loại bỏ các từ dừng (Stopwords tiếng Việt như "và", "hoặc", "thì") — quy trình tiền xử lý văn bản NLP</v>
       </c>
       <c r="F20" t="str">
-        <v>Dịch toàn bộ văn bản sang tiếng Anh bằng API dịch máy, sau đó ép kiểu dữ liệu sang dạng số nguyên — dịch thuật ép kiểu</v>
+        <v>Mã hóa toàn bộ văn bản thành các chuỗi số nhị phân MD5 để bảo mật thông tin khách hàng — mã hóa MD5</v>
       </c>
       <c r="G20" t="str">
         <v>Xóa bỏ toàn bộ các câu văn có độ dài trên 20 từ để tiết kiệm bộ nhớ RAM khi chạy thuật toán — cắt ngắn văn bản cưỡng bức</v>
       </c>
       <c r="H20" t="str">
-        <v>Mã hóa toàn bộ văn bản thành các chuỗi số nhị phân MD5 để bảo mật thông tin khách hàng — mã hóa MD5</v>
+        <v>Dịch toàn bộ văn bản sang tiếng Anh bằng API dịch máy, sau đó ép kiểu dữ liệu sang dạng số nguyên — dịch thuật ép kiểu</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>Dữ liệu quá lệch sẽ làm mô hình luôn dự báo là "Bình thường" vì độ chính xác vẫn đạt 99.5% nhưng vô dụng vì bỏ sót 100% ca lừa đảo. SMOTE (Synthetic Minority Over-sampling Technique) sinh thêm dữ liệu giả lập dựa trên khoảng cách K-Nearest Neighbors của các mẫu thiểu số thực tế. Bắt buộc phải chia train/test trước khi chạy SMOTE để tránh việc dữ liệu kiểm thử bị rò rỉ vào tập huấn luyện.</v>
       </c>
       <c r="E21" t="str">
-        <v>Áp dụng kỹ thuật lấy mẫu lại (Resampling) bằng cách tăng mẫu thiểu số (Oversampling với thuật toán SMOTE) hoặc giảm mẫu đa số (Undersampling), kết hợp chia tập train/test trước khi xử lý để tránh rò rỉ dữ liệu (Data Leakage) — xử lý mất cân bằng dữ liệu khoa học</v>
+        <v>Sao chép thủ công các dòng dữ liệu lừa đảo lặp đi lặp lại nhiều lần trong file Excel cho đến khi số lượng bằng nhau — sao chép thủ công lặp lại</v>
       </c>
       <c r="F21" t="str">
-        <v>Sao chép thủ công các dòng dữ liệu lừa đảo lặp đi lặp lại nhiều lần trong file Excel cho đến khi số lượng bằng nhau — sao chép thủ công lặp lại</v>
+        <v>Giữ nguyên dữ liệu thô và yêu cầu mô hình AI tự điều chỉnh các tham số trọng số mà không cần xử lý dữ liệu đầu vào — đùn đẩy cho mô hình</v>
       </c>
       <c r="G21" t="str">
         <v>Xóa bớt dữ liệu hồ sơ bình thường đi cho đến khi số lượng bằng đúng số lượng hồ sơ lừa đảo (chỉ giữ lại 0.5% dữ liệu gốc) — undersampling cực đoan mất thông tin</v>
       </c>
       <c r="H21" t="str">
-        <v>Giữ nguyên dữ liệu thô và yêu cầu mô hình AI tự điều chỉnh các tham số trọng số mà không cần xử lý dữ liệu đầu vào — đùn đẩy cho mô hình</v>
+        <v>Áp dụng kỹ thuật lấy mẫu lại (Resampling) bằng cách tăng mẫu thiểu số (Oversampling với thuật toán SMOTE) hoặc giảm mẫu đa số (Undersampling), kết hợp chia tập train/test trước khi xử lý để tránh rò rỉ dữ liệu (Data Leakage) — xử lý mất cân bằng dữ liệu khoa học</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>MAR (Khuyết ngẫu nhiên) xảy ra khi xác suất khuyết của biến Y phụ thuộc vào một biến khác X đã quan sát được (ở đây, việc khuyết Cân nặng phụ thuộc vào Tuổi và Giới tính). Vì thế, dùng MICE/Hồi quy dựa trên X để dự báo Y sẽ cho kết quả điền khuyết có độ tin cậy cao nhất, tránh thiên lệch hệ thống.</v>
       </c>
       <c r="E22" t="str">
+        <v>Đây là lỗi hệ thống nhập liệu phần mềm; giải pháp là khóa tài khoản của các bác sĩ đã nhập liệu thiếu thông tin bệnh nhân — kỷ luật nhân sự</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Missing Not at Random (MNAR) vì việc thiếu dữ liệu hoàn toàn không liên quan gì đến các biến khác; giải pháp là điền số 0 vào tất cả các ô bị trống — điền số 0 phá vỡ phân phối</v>
+      </c>
+      <c r="G22" t="str">
         <v>Missing at Random (MAR) vì xác suất khuyết phụ thuộc vào biến quan sát được là Giới tính và Độ tuổi; giải pháp tối ưu là điền khuyết bằng mô hình hồi quy đa biến (như MICE) sử dụng thông tin tuổi và giới tính để dự báo — MAR điền khuyết đa biến</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>Missing Completely at Random (MCAR) vì việc khuyết thiếu hoàn toàn ngẫu nhiên không theo quy luật nào; giải pháp là xóa bỏ hoàn toàn các dòng bị thiếu — xóa dòng khuyết sai cơ chế</v>
       </c>
-      <c r="G22" t="str">
-        <v>Missing Not at Random (MNAR) vì việc thiếu dữ liệu hoàn toàn không liên quan gì đến các biến khác; giải pháp là điền số 0 vào tất cả các ô bị trống — điền số 0 phá vỡ phân phối</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Đây là lỗi hệ thống nhập liệu phần mềm; giải pháp là khóa tài khoản của các bác sĩ đã nhập liệu thiếu thông tin bệnh nhân — kỷ luật nhân sự</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1065,10 +1065,10 @@
         <v>Xảy ra khi các thông tin của tập kiểm thử (Test set) vô tình được đưa vào để tính toán các tham số tiền xử lý (như tính Mean để fillna hoặc Min/Max để Scaling) của tập huấn luyện (Train set); phòng tránh bằng cách chia tập Train/Test trước và chỉ chạy hàm `.fit_transform()` trên tập Train, sau đó áp dụng `.transform()` lên tập Test — ngăn chặn rò rỉ thông tin tập test</v>
       </c>
       <c r="F23" t="str">
+        <v>Xảy ra khi lập trình viên quên không lưu tệp tin code sau khi hoàn thành công việc dọn dẹp dữ liệu — mất mát mã nguồn</v>
+      </c>
+      <c r="G23" t="str">
         <v>Xảy ra khi cơ sở dữ liệu của dự án bị hacker tấn công và lấy trộm thông tin khách hàng ra ngoài; phòng tránh bằng cách cài đặt tường lửa — bảo mật an ninh mạng</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Xảy ra khi lập trình viên quên không lưu tệp tin code sau khi hoàn thành công việc dọn dẹp dữ liệu — mất mát mã nguồn</v>
       </c>
       <c r="H23" t="str">
         <v>Xảy ra khi dữ liệu số bị tràn bộ nhớ do kiểu dữ liệu khai báo quá nhỏ so với giá trị thực tế — tràn bộ nhớ dữ liệu</v>
@@ -1091,19 +1091,19 @@
         <v>Mã bưu chính, mã tỉnh thành (ví dụ mã tỉnh `01`), số điện thoại không phải là số để tính toán mà là mã định danh dạng chuỗi (Text). Nếu lưu kiểu Numeric (int), các chữ số 0 ở đầu (Leading zeros) sẽ tự động bị lược bỏ. Cần ép kiểu String và dùng zfill (zero fill)/LPAD để khôi phục cấu trúc chuẩn.</v>
       </c>
       <c r="E24" t="str">
+        <v>Yêu cầu khách hàng tự viết đơn giải trình lý do tại sao mã bưu chính của họ lại thiếu chữ số 0 — yêu cầu khách hàng giải trình</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Tự động cộng thêm 90000 vào tất cả các giá trị mã bưu chính nhỏ hơn 100000 để đưa chúng về độ dài 6 chữ số — cộng hằng số sai lệch logic</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Xóa bỏ toàn bộ các mã bưu chính bị thiếu số 0 ở đầu vì đây là dữ liệu lỗi không thể phục hồi — xóa bỏ dữ liệu lỗi đầu số</v>
+      </c>
+      <c r="H24" t="str">
         <v>Ép kiểu dữ liệu cột sang dạng chuỗi ký tự (String/Text), sau đó sử dụng hàm chèn đệm (như `.str.zfill(6)` trong Python hoặc LPAD trong SQL) để tự động thêm chữ số 0 vào đầu cho đủ độ dài quy định — hàm chèn đệm LPAD/zfill</v>
       </c>
-      <c r="F24" t="str">
-        <v>Xóa bỏ toàn bộ các mã bưu chính bị thiếu số 0 ở đầu vì đây là dữ liệu lỗi không thể phục hồi — xóa bỏ dữ liệu lỗi đầu số</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Tự động cộng thêm 90000 vào tất cả các giá trị mã bưu chính nhỏ hơn 100000 để đưa chúng về độ dài 6 chữ số — cộng hằng số sai lệch logic</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Yêu cầu khách hàng tự viết đơn giải trình lý do tại sao mã bưu chính của họ lại thiếu chữ số 0 — yêu cầu khách hàng giải trình</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Trong phân tích cảm xúc (Sentiment Analysis), emoji mang thông điệp rất mạnh mẽ (thậm chí mạnh hơn chữ viết). Việc chuyển đổi emoji sang text tương đương (Emoji-to-text mapping) giúp giữ lại các sắc thái cảm xúc quan trọng cho thuật toán xử lý ngôn ngữ tự nhiên.</v>
       </c>
       <c r="E25" t="str">
-        <v>Chuyển đổi các emoji phổ biến thành các từ mang ý nghĩa tương ứng (ví dụ: 😊 thành "vui/hài lòng", 😢 thành "buồn/thất vọng") để mô hình NLP đọc hiểu được, hoặc loại bỏ hoàn toàn các emoji không có ý nghĩa phân tích — chuẩn hóa chuyển đổi emoji</v>
+        <v>Xóa bỏ toàn bộ bài viết nếu bài viết đó có chứa bất kỳ ký tự emoji nào — xóa bỏ bài viết chứa emoji</v>
       </c>
       <c r="F25" t="str">
-        <v>Xóa bỏ toàn bộ bài viết nếu bài viết đó có chứa bất kỳ ký tự emoji nào — xóa bỏ bài viết chứa emoji</v>
+        <v>Yêu cầu khách hàng không được phép sử dụng các biểu tượng cảm xúc khi viết đánh giá trên ứng dụng di động — hạn chế người dùng</v>
       </c>
       <c r="G25" t="str">
         <v>Giữ nguyên emoji và ép kiểu dữ liệu của cột review sang dạng số thực float — ép kiểu float sai lệch</v>
       </c>
       <c r="H25" t="str">
-        <v>Yêu cầu khách hàng không được phép sử dụng các biểu tượng cảm xúc khi viết đánh giá trên ứng dụng di động — hạn chế người dùng</v>
+        <v>Chuyển đổi các emoji phổ biến thành các từ mang ý nghĩa tương ứng (ví dụ: 😊 thành "vui/hài lòng", 😢 thành "buồn/thất vọng") để mô hình NLP đọc hiểu được, hoặc loại bỏ hoàn toàn các emoji không có ý nghĩa phân tích — chuẩn hóa chuyển đổi emoji</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Khi hai biến tương quan quá mạnh (ví dụ: Chiều cao và Chiều dài chân), mô hình hồi quy tuyến tính không thể phân biệt được biến nào thực sự tác động đến kết quả. DA phải kiểm tra hệ số VIF (Variance Inflation Factor), nếu VIF &gt; 5-10 thì cần loại bỏ bớt một trong các biến tương quan mạnh đó.</v>
       </c>
       <c r="E26" t="str">
+        <v>Vì đa cộng tuyến tự động làm tăng dung lượng lưu trữ của tệp tin database lên gấp 10 lần — tăng bộ nhớ lưu trữ</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Vì đa cộng tuyến làm sập máy chủ chạy thuật toán do tràn bộ nhớ RAM của vi xử lý — tràn bộ nhớ RAM</v>
+      </c>
+      <c r="G26" t="str">
         <v>Vì đa cộng tuyến làm mất tính ổn định của các hệ số hồi quy (coefficients), khiến mô hình khó xác định chính xác mức độ tác động riêng biệt của từng biến lên biến mục tiêu — mất tính ổn định hệ số</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Vì đa cộng tuyến tự động làm tăng dung lượng lưu trữ của tệp tin database lên gấp 10 lần — tăng bộ nhớ lưu trữ</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Vì đa cộng tuyến làm sập máy chủ chạy thuật toán do tràn bộ nhớ RAM của vi xử lý — tràn bộ nhớ RAM</v>
       </c>
       <c r="H26" t="str">
         <v>Vì đa cộng tuyến là yêu cầu bảo mật thông tin bắt buộc đối với các dự án y tế và tài chính — bảo mật thông tin</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
